--- a/99_tips/QCAコーディング作業用.xlsx
+++ b/99_tips/QCAコーディング作業用.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_qca\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyama\Documents\r_analysis\miyagi-agricultural-recovery\99_tips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145ED627-6616-42CD-AB61-B086BCD94120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B015109D-C7D0-4135-B695-88EC5BFFAE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>no</t>
     <phoneticPr fontId="3"/>
@@ -295,6 +292,14 @@
   </si>
   <si>
     <t>渡辺庄哉</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>mechcap2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>agecap2</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -635,17 +640,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.58203125" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" customWidth="1"/>
-    <col min="7" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.296875" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" customWidth="1"/>
+    <col min="5" max="6" width="14.09765625" customWidth="1"/>
+    <col min="8" max="8" width="14.19921875" customWidth="1"/>
+    <col min="9" max="11" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -662,25 +668,31 @@
         <v>22</v>
       </c>
       <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>19</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -706,13 +718,19 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
@@ -729,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -743,8 +761,14 @@
       <c r="J3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
@@ -775,8 +799,14 @@
       <c r="J4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
@@ -796,19 +826,25 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
@@ -825,22 +861,28 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
@@ -857,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -871,8 +913,14 @@
       <c r="J7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>7</v>
       </c>
@@ -886,13 +934,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -903,8 +951,14 @@
       <c r="J8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>8</v>
       </c>
@@ -921,10 +975,10 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -935,8 +989,14 @@
       <c r="J9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>9</v>
       </c>
@@ -953,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -967,8 +1027,14 @@
       <c r="J10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>10</v>
       </c>
@@ -985,22 +1051,28 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1020,19 +1092,25 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1055,16 +1133,22 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>17</v>
       </c>
@@ -1084,19 +1168,25 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>18</v>
       </c>
@@ -1110,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1122,13 +1212,19 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>19</v>
       </c>
@@ -1145,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1159,126 +1255,132 @@
       <c r="J16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>16</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K21">
-      <sortCondition descending="1" ref="J1:J21"/>
+  <autoFilter ref="A1:M21" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M21">
+      <sortCondition descending="1" ref="L1:L21"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3"/>

--- a/99_tips/QCAコーディング作業用.xlsx
+++ b/99_tips/QCAコーディング作業用.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyama\Documents\r_analysis\miyagi-agricultural-recovery\99_tips\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\miyagi-agricultural-recovery\miyagi-agricultural-recovery\99_tips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B015109D-C7D0-4135-B695-88EC5BFFAE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D909D5-F6B8-4A2E-9BE8-3DFC1FEF372F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>no</t>
     <phoneticPr fontId="3"/>
@@ -300,6 +303,16 @@
   </si>
   <si>
     <t>agecap2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>largescale</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>largescale2</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -358,8 +371,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -640,18 +656,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="9.296875" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" customWidth="1"/>
-    <col min="5" max="6" width="14.09765625" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" customWidth="1"/>
-    <col min="9" max="11" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.69921875" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.58203125" customWidth="1"/>
+    <col min="5" max="6" width="14.08203125" customWidth="1"/>
+    <col min="8" max="10" width="14.1640625" customWidth="1"/>
+    <col min="11" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -676,23 +692,29 @@
       <c r="H1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>19</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>20</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -717,20 +739,26 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+      <c r="I2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="1">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -755,10 +783,10 @@
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1">
         <v>1</v>
       </c>
       <c r="K3">
@@ -767,8 +795,14 @@
       <c r="L3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -793,10 +827,10 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="K4">
@@ -805,8 +839,14 @@
       <c r="L4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -831,20 +871,26 @@
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -869,20 +915,26 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -907,11 +959,11 @@
       <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -919,8 +971,14 @@
       <c r="L7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -945,11 +1003,11 @@
       <c r="H8">
         <v>1</v>
       </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -957,8 +1015,14 @@
       <c r="L8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -983,11 +1047,11 @@
       <c r="H9">
         <v>1</v>
       </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -995,8 +1059,14 @@
       <c r="L9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1021,11 +1091,11 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1033,8 +1103,14 @@
       <c r="L10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1059,20 +1135,26 @@
       <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1097,20 +1179,26 @@
       <c r="H12">
         <v>1</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1135,20 +1223,26 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>17</v>
       </c>
@@ -1173,20 +1267,26 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>18</v>
       </c>
@@ -1211,20 +1311,26 @@
       <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
         <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>19</v>
       </c>
@@ -1249,11 +1355,11 @@
       <c r="H16">
         <v>1</v>
       </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1261,126 +1367,132 @@
       <c r="L16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
       <c r="K18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>16</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M21" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M21">
-      <sortCondition descending="1" ref="L1:L21"/>
+  <autoFilter ref="A1:O21" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O21">
+      <sortCondition descending="1" ref="N1:N21"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3"/>

--- a/99_tips/QCAコーディング作業用.xlsx
+++ b/99_tips/QCAコーディング作業用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\miyagi-agricultural-recovery\miyagi-agricultural-recovery\99_tips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D909D5-F6B8-4A2E-9BE8-3DFC1FEF372F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8789845-14C0-4B52-A2D2-F37EA2EFD313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
